--- a/docs/project-checklists.xlsx
+++ b/docs/project-checklists.xlsx
@@ -4897,6 +4897,100 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Marketing Site</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Landing page redesign completed</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Current landing page is not yet strong enough for premium product positioning</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Run a full brand and conversion redesign later</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Positioning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Product messaging and trust-signals upgraded</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Rewrite positioning and supporting sections</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -5895,12 +5989,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tune Civis AI quality for live users</t>
+          <t>Redesign landing page and premium positioning</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Product + Engineering</t>
+          <t>Product + Design + Engineering</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5910,44 +6004,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Stable AI provider configuration</t>
+          <t>Core platform credibility first</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>AI is materially improved but still needs polish</t>
+          <t>The current landing page does not yet match the quality of the product ambition</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Collect real prompts and refine responses</t>
+          <t>Treat it as a dedicated brand/conversion redesign later</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Execute NDPA/VAPT hardening backlog</t>
+          <t>Tune Civis AI quality for live users</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Engineering + Security</t>
+          <t>Product + Engineering</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5957,12 +6051,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5972,62 +6066,109 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Security docs already created</t>
+          <t>Stable AI provider configuration</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Architecture and API docs exist; implementation backlog remains</t>
+          <t>AI is materially improved but still needs polish</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Prioritize access control, monitoring, and incident readiness</t>
+          <t>Collect real prompts and refine responses</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Execute NDPA/VAPT hardening backlog</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Engineering + Security</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Security docs already created</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Architecture and API docs exist; implementation backlog remains</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Prioritize access control, monitoring, and incident readiness</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Keep documentation and OpenAPI in sync</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Ongoing</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Feature shipping discipline</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Docs exist and should now be maintained with each batch</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Make docs updates part of release definition</t>
         </is>
@@ -11086,6 +11227,100 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Marketing Site</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Landing page redesign completed</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Current landing page is not yet strong enough for premium product positioning</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Run a full brand and conversion redesign later</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Phase 17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Positioning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Product messaging and trust-signals upgraded</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Rewrite positioning and supporting sections</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -11990,6 +12225,38 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Landing page and marketing-site redesign</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Important for conversion and brand perception, but not the first platform blocker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/project-checklists.xlsx
+++ b/docs/project-checklists.xlsx
@@ -1,16 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookViews>
-    <workbookView/>
-  </workbookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
     <sheet name="Executive" sheetId="2" r:id="rId2"/>
     <sheet name="Done" sheetId="3" r:id="rId3"/>
     <sheet name="In Progress" sheetId="4" r:id="rId4"/>
     <sheet name="Pending" sheetId="5" r:id="rId5"/>
-    <sheet name="Pitch Readiness" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -20,7 +16,7 @@
   <fonts count="1">
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,7 +50,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3651,12 +3646,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Local only</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3666,12 +3661,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Stakeholder admins can be created, but acceptance/onboarding is not finished</t>
+          <t>Invite issuance, lookup, re-invite, and signup completion now exist locally</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Build invite acceptance and completion flow</t>
+          <t>Deploy and smoke-test stakeholder onboarding flow</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4992,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -5670,7 +5664,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5685,7 +5679,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Local only</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5695,12 +5689,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Stakeholder admins need a complete acceptance and workspace-lifecycle flow, not just seeded records</t>
+          <t>Invite acceptance is now built locally; deploy validation and broader lifecycle controls still remain</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Prioritize invite acceptance and org lifecycle controls</t>
+          <t>Deploy and validate stakeholder onboarding, then extend org lifecycle controls</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6174,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8303,7 +8296,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -8741,12 +8733,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Workspace Provisioning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Founder lock and workspace-scoped admin boundaries started</t>
+          <t>Invite acceptance flow for seeded users implemented</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8766,34 +8758,34 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Role boundaries now exist in admin flows, but action-level RBAC is not complete</t>
+          <t>Invite issuance, lookup, re-invite, and signup completion now exist locally</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Extend into module-by-module permission enforcement</t>
+          <t>Deploy and smoke-test stakeholder onboarding flow</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Phase 8</t>
+          <t>Phase 12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Tenant Lifecycle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Backend Conversion</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HR API routes added (employees, payroll, attendance, positions)</t>
+          <t>Founder lock and workspace-scoped admin boundaries started</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -8813,12 +8805,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Routes exist in local worktree</t>
+          <t>Role boundaries now exist in admin flows, but action-level RBAC is not complete</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Apply migration, test, then commit</t>
+          <t>Extend into module-by-module permission enforcement</t>
         </is>
       </c>
     </row>
@@ -8835,12 +8827,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Frontend Rewire</t>
+          <t>Backend Conversion</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HR page rewritten to call /api/hr/*</t>
+          <t>HR API routes added (employees, payroll, attendance, positions)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8860,12 +8852,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>UI is being moved off mock/local-only state</t>
+          <t>Routes exist in local worktree</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Validate with live DB</t>
+          <t>Apply migration, test, then commit</t>
         </is>
       </c>
     </row>
@@ -8882,12 +8874,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Data Quality</t>
+          <t>Frontend Rewire</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HR scorecard/compliance views present</t>
+          <t>HR page rewritten to call /api/hr/*</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8902,17 +8894,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Support components exist locally</t>
+          <t>UI is being moved off mock/local-only state</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Finish polish and validation</t>
+          <t>Validate with live DB</t>
         </is>
       </c>
     </row>
@@ -8924,17 +8916,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Backend Conversion</t>
+          <t>Data Quality</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projects API routes added</t>
+          <t>HR scorecard/compliance views present</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8949,17 +8941,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>/api/projects and /api/projects/tasks exist locally</t>
+          <t>Support components exist locally</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Apply migration, test, then commit</t>
+          <t>Finish polish and validation</t>
         </is>
       </c>
     </row>
@@ -8976,12 +8968,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frontend Rewire</t>
+          <t>Backend Conversion</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Projects page rewritten to use live API</t>
+          <t>Projects API routes added</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -9001,12 +8993,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Project board/task/timeline are wired toward live data</t>
+          <t>/api/projects and /api/projects/tasks exist locally</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Validate with live DB</t>
+          <t>Apply migration, test, then commit</t>
         </is>
       </c>
     </row>
@@ -9018,17 +9010,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Projects</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Backend Conversion</t>
+          <t>Frontend Rewire</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Inventory API routes added</t>
+          <t>Projects page rewritten to use live API</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9048,12 +9040,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Products, stock, orders routes exist locally</t>
+          <t>Project board/task/timeline are wired toward live data</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Apply migration, test, then commit</t>
+          <t>Validate with live DB</t>
         </is>
       </c>
     </row>
@@ -9070,12 +9062,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frontend Rewire</t>
+          <t>Backend Conversion</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Inventory page rewritten to use live API</t>
+          <t>Inventory API routes added</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -9095,12 +9087,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tables are wired toward live data</t>
+          <t>Products, stock, orders routes exist locally</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Validate with live DB</t>
+          <t>Apply migration, test, then commit</t>
         </is>
       </c>
     </row>
@@ -9112,17 +9104,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shared Backend</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seed Data</t>
+          <t>Frontend Rewire</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Module seed helper added for HR/Projects/Inventory</t>
+          <t>Inventory page rewritten to use live API</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9137,17 +9129,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Local seed helper exists</t>
+          <t>Tables are wired toward live data</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Keep only as controlled dev/demo behavior</t>
+          <t>Validate with live DB</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9156,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Access Control</t>
+          <t>Seed Data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Org ownership checks added to new HR/Projects/Inventory routes</t>
+          <t>Module seed helper added for HR/Projects/Inventory</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9184,62 +9176,109 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mutation routes were tightened locally</t>
+          <t>Local seed helper exists</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Ship with backend conversion commit</t>
+          <t>Keep only as controlled dev/demo behavior</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Phase 8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Shared Backend</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Access Control</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Org ownership checks added to new HR/Projects/Inventory routes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Local only</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Mutation routes were tightened locally</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Ship with backend conversion commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Phase 9</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Pending migration created for HR/Projects/Inventory backend</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Local only</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Migration folder exists locally</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Apply migration to active database</t>
         </is>
@@ -9251,7 +9290,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -9971,12 +10009,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Workspace Provisioning</t>
+          <t>Workspace Access</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Invite acceptance flow for seeded users implemented</t>
+          <t>Multi-workspace membership and org switching implemented</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -9996,12 +10034,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Stakeholder admins can be created, but acceptance/onboarding is not finished</t>
+          <t>Founder/support workflows will need to move across workspaces cleanly</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Build invite acceptance and completion flow</t>
+          <t>Design membership model and switcher</t>
         </is>
       </c>
     </row>
@@ -10018,12 +10056,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Workspace Access</t>
+          <t>Workspace Governance</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Multi-workspace membership and org switching implemented</t>
+          <t>Workspace suspension, archive, and restore controls implemented</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10038,17 +10076,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Founder/support workflows will need to move across workspaces cleanly</t>
+          <t>You need a lifecycle for dormant or non-compliant stakeholder orgs</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Design membership model and switcher</t>
+          <t>Add org status controls and UI</t>
         </is>
       </c>
     </row>
@@ -10065,12 +10103,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Workspace Governance</t>
+          <t>Entitlements</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Workspace suspension, archive, and restore controls implemented</t>
+          <t>Org-level feature flags and lifecycle states implemented</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -10090,12 +10128,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>You need a lifecycle for dormant or non-compliant stakeholder orgs</t>
+          <t>Required for staged rollout and plan control</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Add org status controls and UI</t>
+          <t>Add feature flag and org state model</t>
         </is>
       </c>
     </row>
@@ -10112,12 +10150,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Entitlements</t>
+          <t>Authorization</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Org-level feature flags and lifecycle states implemented</t>
+          <t>Action-level RBAC matrix enforced across modules</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10132,39 +10170,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Required for staged rollout and plan control</t>
+          <t>Current auth is stronger, but not yet a full action matrix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Add feature flag and org state model</t>
+          <t>Define and enforce per-action permissions</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Phase 12</t>
+          <t>Phase 13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tenant Lifecycle</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Billing</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Action-level RBAC matrix enforced across modules</t>
+          <t>Seat and entitlement model implemented</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10179,17 +10217,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Current auth is stronger, but not yet a full action matrix</t>
+          <t>Stakeholder workspaces need plan-aware limits</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Define and enforce per-action permissions</t>
+          <t>Define seat model and enforcement</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10249,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Seat and entitlement model implemented</t>
+          <t>Billing and subscription admin console implemented</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10231,12 +10269,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Stakeholder workspaces need plan-aware limits</t>
+          <t>Admins need visibility into plan and seats</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Define seat model and enforcement</t>
+          <t>Build billing summary and controls</t>
         </is>
       </c>
     </row>
@@ -10253,12 +10291,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Billing</t>
+          <t>Feature Gating</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Billing and subscription admin console implemented</t>
+          <t>Plan-aware feature gating implemented</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10278,12 +10316,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Admins need visibility into plan and seats</t>
+          <t>Needed to sell multiple tiers without code forks</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Build billing summary and controls</t>
+          <t>Add entitlements to routes and UI</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10338,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Feature Gating</t>
+          <t>Lifecycle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Plan-aware feature gating implemented</t>
+          <t>Trial, upgrade, and downgrade flows implemented</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10320,39 +10358,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Needed to sell multiple tiers without code forks</t>
+          <t>Commercial readiness improves with self-service lifecycle</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Add entitlements to routes and UI</t>
+          <t>Add commercial lifecycle rules</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Phase 13</t>
+          <t>Phase 14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lifecycle</t>
+          <t>Observability</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Trial, upgrade, and downgrade flows implemented</t>
+          <t>Production error tracking and alerting configured</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10367,17 +10405,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Commercial readiness improves with self-service lifecycle</t>
+          <t>You should know when auth, AI, uploads, or DB fail in production</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Add commercial lifecycle rules</t>
+          <t>Configure monitoring and alerting</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10437,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Production error tracking and alerting configured</t>
+          <t>Structured logs and uptime monitoring configured</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10414,17 +10452,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>You should know when auth, AI, uploads, or DB fail in production</t>
+          <t>Support and operations need visibility into live failures</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Configure monitoring and alerting</t>
+          <t>Add log aggregation and uptime checks</t>
         </is>
       </c>
     </row>
@@ -10441,12 +10479,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Observability</t>
+          <t>Async Work</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Structured logs and uptime monitoring configured</t>
+          <t>Background jobs and queue system implemented</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10466,12 +10504,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Support and operations need visibility into live failures</t>
+          <t>Digests, webhooks, and retries should not depend on request-response timing</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Add log aggregation and uptime checks</t>
+          <t>Add async job infrastructure</t>
         </is>
       </c>
     </row>
@@ -10488,12 +10526,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Async Work</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Background jobs and queue system implemented</t>
+          <t>Backup and restore workflow documented and tested</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -10508,17 +10546,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Digests, webhooks, and retries should not depend on request-response timing</t>
+          <t>Production data safety is not optional</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Add async job infrastructure</t>
+          <t>Define backup plan and run restore drills</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10578,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Backup and restore workflow documented and tested</t>
+          <t>Incident response runbook operationalized</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -10555,39 +10593,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Production data safety is not optional</t>
+          <t>The docs exist, but the operating motion does not yet</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Define backup plan and run restore drills</t>
+          <t>Create and test response workflow</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Phase 14</t>
+          <t>Phase 15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Data Governance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Import/Export</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Incident response runbook operationalized</t>
+          <t>CSV importers for CRM, HR, inventory, and accounting implemented</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -10607,12 +10645,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The docs exist, but the operating motion does not yet</t>
+          <t>Real customers will want to move data in fast</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Create and test response workflow</t>
+          <t>Build import tools and mapping UX</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10672,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CSV importers for CRM, HR, inventory, and accounting implemented</t>
+          <t>Admin export center for operational and compliance data implemented</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -10654,12 +10692,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Real customers will want to move data in fast</t>
+          <t>Stakeholders will need consistent exports beyond isolated reports</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Build import tools and mapping UX</t>
+          <t>Add central export surface</t>
         </is>
       </c>
     </row>
@@ -10676,12 +10714,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Import/Export</t>
+          <t>Recovery</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Admin export center for operational and compliance data implemented</t>
+          <t>Soft delete and record recovery flows implemented</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -10701,12 +10739,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Stakeholders will need consistent exports beyond isolated reports</t>
+          <t>Accidental deletion without recovery will hurt trust</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Add central export surface</t>
+          <t>Add reversible delete patterns</t>
         </is>
       </c>
     </row>
@@ -10723,12 +10761,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Recovery</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Soft delete and record recovery flows implemented</t>
+          <t>Data retention and purge controls implemented</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -10748,12 +10786,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Accidental deletion without recovery will hurt trust</t>
+          <t>Needed for governance and NDPA discipline</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Add reversible delete patterns</t>
+          <t>Define retention policy and jobs</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10813,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Data retention and purge controls implemented</t>
+          <t>NDPA/privacy request workflow implemented</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -10795,12 +10833,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Needed for governance and NDPA discipline</t>
+          <t>Privacy requests should be operational, not only documented</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Define retention policy and jobs</t>
+          <t>Add request handling workflow</t>
         </is>
       </c>
     </row>
@@ -10817,12 +10855,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NDPA/privacy request workflow implemented</t>
+          <t>Approval center for sensitive actions implemented</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -10842,12 +10880,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Privacy requests should be operational, not only documented</t>
+          <t>High-risk actions need approvals and evidence</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Add request handling workflow</t>
+          <t>Build approval center and audit tie-in</t>
         </is>
       </c>
     </row>
@@ -10864,12 +10902,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Branding</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Approval center for sensitive actions implemented</t>
+          <t>White-label and enterprise branding controls implemented</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -10884,39 +10922,39 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>High-risk actions need approvals and evidence</t>
+          <t>Important for polished stakeholder rollout, but not a launch blocker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Build approval center and audit tie-in</t>
+          <t>Add branding controls later</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Phase 15</t>
+          <t>Phase 16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Data Governance</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Branding</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>White-label and enterprise branding controls implemented</t>
+          <t>In-product help center and onboarding content implemented</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -10936,12 +10974,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Important for polished stakeholder rollout, but not a launch blocker</t>
+          <t>Users need a support surface that does not depend on you manually answering everything</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Add branding controls later</t>
+          <t>Build help center and guides</t>
         </is>
       </c>
     </row>
@@ -10958,12 +10996,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Support Ops</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>In-product help center and onboarding content implemented</t>
+          <t>Support impersonation with audit trail implemented</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -10978,17 +11016,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Users need a support surface that does not depend on you manually answering everything</t>
+          <t>Support needs controlled access for troubleshooting</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Build help center and guides</t>
+          <t>Add audited impersonation or support sessions</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11043,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Support Ops</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Support impersonation with audit trail implemented</t>
+          <t>Customer usage and health analytics implemented</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11025,17 +11063,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Support needs controlled access for troubleshooting</t>
+          <t>Useful for renewals and stakeholder expansion</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Add audited impersonation or support sessions</t>
+          <t>Add adoption and health reporting</t>
         </is>
       </c>
     </row>
@@ -11052,12 +11090,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Customer usage and health analytics implemented</t>
+          <t>Release notes and changelog workflow implemented</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -11077,12 +11115,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Useful for renewals and stakeholder expansion</t>
+          <t>Customers should see product progress clearly</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Add adoption and health reporting</t>
+          <t>Add changelog discipline</t>
         </is>
       </c>
     </row>
@@ -11094,17 +11132,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Go-To-Market</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Release notes and changelog workflow implemented</t>
+          <t>Accessibility and mobile QA sweep completed</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -11119,17 +11157,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Customers should see product progress clearly</t>
+          <t>Pitching stakeholders on unstable mobile/accessibility experiences is risky</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Add changelog discipline</t>
+          <t>Run QA sweep and fix findings</t>
         </is>
       </c>
     </row>
@@ -11146,12 +11184,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Readiness</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Accessibility and mobile QA sweep completed</t>
+          <t>Stakeholder pitch readiness gate completed</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -11166,39 +11204,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pitching stakeholders on unstable mobile/accessibility experiences is risky</t>
+          <t>You need a formal go/no-go checklist before handing this to serious stakeholders</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Run QA sweep and fix findings</t>
+          <t>Use the pitch-readiness document as the gate</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Phase 16</t>
+          <t>Phase 17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Go-To-Market</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Readiness</t>
+          <t>Marketing Site</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Stakeholder pitch readiness gate completed</t>
+          <t>Landing page redesign completed</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -11213,17 +11251,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>You need a formal go/no-go checklist before handing this to serious stakeholders</t>
+          <t>Current landing page is not yet strong enough for premium product positioning</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Use the pitch-readiness document as the gate</t>
+          <t>Run a full brand and conversion redesign later</t>
         </is>
       </c>
     </row>
@@ -11240,12 +11278,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Marketing Site</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Landing page redesign completed</t>
+          <t>Product messaging and trust-signals upgraded</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11265,995 +11303,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Current landing page is not yet strong enough for premium product positioning</t>
+          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Run a full brand and conversion redesign later</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Phase 17</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Positioning</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Product messaging and trust-signals upgraded</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>The product needs clearer premium positioning for stakeholders and buyers</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
           <t>Rewrite positioning and supporting sections</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Platform Control</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Founder remains the only permanent SUPER_ADMIN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Policy and local enforcement exist; must be validated on live deploy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Platform Control</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Stakeholder admins are restricted to their own workspace</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Admin boundaries exist locally; validate on live deploy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Platform Control</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Admin pages are live on deployed environment</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>New control plane is local until committed and deployed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Platform Control</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Workspace admin user management works on deployed environment</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Needs live validation after deploy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Data and Backend</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Database connection is stable and reachable</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Current DB connectivity is the main blocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Data and Backend</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pending migrations are applied successfully</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Required before broader live validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Data and Backend</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Core module data persists correctly against live DB</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HR, Projects, Inventory still need end-to-end live validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Security Baseline</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Role boundaries are enforced server-side</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Improved locally; still needs broader module-by-module hardening</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Security Baseline</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Audit logs capture admin-critical actions</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Admin actions now audit locally; validate and broaden coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Must Have</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Product Stability</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Critical pages do not throw runtime errors in demo path</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Production build passes; still validate deployed flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Identity and Access</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Invite acceptance flow for seeded users</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Stakeholder onboarding needs completion flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Identity and Access</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Stable Google OAuth or clearly supported credentials flow</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Decide the production sign-in path and validate it</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Identity and Access</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Full 2FA validation against live database</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Route surface exists; live validation still needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Production Integrations</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SMTP configured and tested</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Required for notifications and digests</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Production Integrations</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cloudinary or equivalent upload storage configured and tested</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Required for portal/docs/gallery upload credibility</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Error tracking configured</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>You need visibility into production failures</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Backup and restore plan tested</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Production data safety must be operational</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Should Have Before Paid Pilot</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Security hardening backlog started in implementation</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NDPA/VAPT should move from docs into code/ops</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pitch-Ready Next</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Data Governance</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CSV importers for CRM/HR/Inventory/Accounting</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Important for real onboarding speed</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pitch-Ready Next</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Data Governance</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Export center for operational/compliance workflows</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Stakeholders will ask for reliable exports</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pitch-Ready Next</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Recovery</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Soft delete and record recovery</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Protects trust after mistakes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pitch-Ready Next</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>In-product help center</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Reduces dependence on founder support</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pitch-Ready Next</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Support impersonation with audit trail</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Important for troubleshooting and customer success</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Pitch-Ready Next</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Billing and seat visibility for admins</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Important as soon as pricing is formalized</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Later</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Enterprise</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>White-label and enterprise branding controls</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Useful for premium deals but not first blocker</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Later</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Advanced subscription self-service</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Can follow initial controlled rollout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Later</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Expanded approval center for sensitive actions</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Important as complexity grows</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Later</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Landing page and marketing-site redesign</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Important for conversion and brand perception, but not the first platform blocker</t>
         </is>
       </c>
     </row>
